--- a/士兵数据配置.xlsx
+++ b/士兵数据配置.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1\个人作品集\游戏制作\battle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEBF7582-6FF7-4E67-9F85-9561D3151B60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D560D9EB-D6B4-47EA-8E20-2F2AB74F13D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,9 +65,6 @@
     <t>矛兵 (SPEARMAN)</t>
   </si>
   <si>
-    <t>高爆发, 冲锋, 刺客型</t>
-  </si>
-  <si>
     <t>空位 (BLANK)</t>
   </si>
   <si>
@@ -164,10 +161,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1.优先攻击血量最低的敌人2.当战场上存在右方剑盾兵时，躲在剑盾兵后进行攻击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1.开局冲锋到地方后排，并撞飞中途的敌人，如果对方也是矛兵，则双方不会被击飞</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -180,11 +173,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>高爆发，冲刺，累计奔跑值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.开局奔跑值100，会从两侧向地方后排冲刺，并附带击退效果，中途不会停止，会一路冲回友方后排2.非攻击进行奔跑时会累计奔跑值，每0.1秒增加10点奔跑值，当奔跑值大于等于50时骑兵可以冲撞敌人，并附带击退效果，奔跑值越高冲撞伤害越高 3.骑兵倾向于累计更高的奔跑值再发动进攻（0.5概率），但也会随机发起冲撞（0.5概率）4.骑兵冲撞后，奔跑值最低降低为10点</t>
+    <t>1.开局时奔跑值为100，然后直接向敌人冲锋直到触碰到地图边界 2.骑兵无法进行近战攻击，当奔跑值小于等于50时，骑兵会尽可能远离敌人到远处，然后奔跑积累奔跑值3.当奔跑值大于50时可以对敌人（优先血量最低敌人）进行冲锋攻击，期间依然可以累计奔跑值 4.当骑兵冲锋后奔跑值降低为10点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高爆发, 冲锋（会将路径上的敌人击飞）, 刺客型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高爆发，冲刺冲锋（会将路径上的敌人击退），累计奔跑值(每10点奔跑值增加0.1像素/秒的移动速度)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.优先攻击血量最低的敌人2.当战场上存在右方剑盾兵时，躲在剑盾兵后进行攻击 3.当战场上不存在剑盾兵时，会尽可能远离敌人（敌人距离自己大于等于100时）再攻击</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -570,13 +571,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="13" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.796875" customWidth="1"/>
-    <col min="2" max="4" width="15.796875" customWidth="1"/>
-    <col min="5" max="8" width="20.796875" customWidth="1"/>
-    <col min="9" max="9" width="40.796875" customWidth="1"/>
-    <col min="10" max="10" width="100.69921875" customWidth="1"/>
+    <col min="8" max="8" width="19.09765625" customWidth="1"/>
+    <col min="9" max="9" width="29.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -599,7 +597,7 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H1" t="s">
         <v>6</v>
@@ -608,7 +606,7 @@
         <v>7</v>
       </c>
       <c r="J1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -631,7 +629,7 @@
         <v>0.8</v>
       </c>
       <c r="G2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H2">
         <v>30</v>
@@ -640,7 +638,7 @@
         <v>10</v>
       </c>
       <c r="J2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -663,7 +661,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H3">
         <v>250</v>
@@ -672,7 +670,7 @@
         <v>12</v>
       </c>
       <c r="J3" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -695,21 +693,21 @@
         <v>1.2</v>
       </c>
       <c r="G4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H4">
         <v>45</v>
       </c>
       <c r="I4" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="J4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -727,7 +725,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H5">
         <v>30</v>
@@ -736,12 +734,12 @@
         <v>49</v>
       </c>
       <c r="J5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -765,17 +763,17 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" t="s">
         <v>16</v>
-      </c>
-      <c r="J6" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A3 D3 A2:B2 D2 A4:D4 H6:J6 F2:F4 A6:F6 A1:F1 H1:I1 H2:I2 H3:I3 H4:I4" numberStoredAsText="1"/>
+    <ignoredError sqref="A3 D3 A2:B2 D2 A4:D4 H6:J6 F2:F4 A6:F6 A1:F1 H1:I1 H2:I2 H3:I3 H4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -783,121 +781,121 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.796875" customWidth="1"/>
     <col min="2" max="2" width="60.796875" customWidth="1"/>
     <col min="3" max="3" width="50.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>19</v>
       </c>
-      <c r="C1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
         <v>21</v>
       </c>
-      <c r="C2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
         <v>23</v>
       </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
         <v>25</v>
       </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
         <v>27</v>
       </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
         <v>29</v>
       </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
         <v>31</v>
       </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
         <v>33</v>
       </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
         <v>35</v>
       </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
         <v>37</v>
-      </c>
-      <c r="C10" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/士兵数据配置.xlsx
+++ b/士兵数据配置.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1\个人作品集\游戏制作\battle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D560D9EB-D6B4-47EA-8E20-2F2AB74F13D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF2E086-3330-4784-B02C-45397AA7D344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="士兵数据" sheetId="1" r:id="rId1"/>
-    <sheet name="字段说明" sheetId="2" r:id="rId2"/>
+    <sheet name="士兵系统" sheetId="1" r:id="rId1"/>
+    <sheet name="技能系统" sheetId="3" r:id="rId2"/>
+    <sheet name="字段说明" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="63">
   <si>
     <t>单位类型</t>
   </si>
@@ -157,10 +158,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1.优先攻击距离自己最近的敌人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1.开局冲锋到地方后排，并撞飞中途的敌人，如果对方也是矛兵，则双方不会被击飞</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -173,10 +170,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1.开局时奔跑值为100，然后直接向敌人冲锋直到触碰到地图边界 2.骑兵无法进行近战攻击，当奔跑值小于等于50时，骑兵会尽可能远离敌人到远处，然后奔跑积累奔跑值3.当奔跑值大于50时可以对敌人（优先血量最低敌人）进行冲锋攻击，期间依然可以累计奔跑值 4.当骑兵冲锋后奔跑值降低为10点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>高爆发, 冲锋（会将路径上的敌人击飞）, 刺客型</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -185,7 +178,63 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1.优先攻击血量最低的敌人2.当战场上存在右方剑盾兵时，躲在剑盾兵后进行攻击 3.当战场上不存在剑盾兵时，会尽可能远离敌人（敌人距离自己大于等于100时）再攻击</t>
+    <t>1.优先攻击血量最低的敌人2.当战场上存在友方剑盾兵时，优先躲在剑盾兵后进行攻击 3.当战场上不存在剑盾兵时，会与敌人保持距离，当敌我距离在75像素到250像素区间时会进行攻击，当敌我距离小于等于75像素时会向四周远离敌人（优先往远离墙壁的方向移动）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.开局时奔跑值为100，然后直接向敌人冲锋直到地方后排 2.骑兵无法进行近战攻击，当奔跑值小于等于50时，骑兵会尽可能远离敌人到远处（向四周移动，优先往远离墙壁的方向奔跑，可以非直线运动），然后奔跑积累奔跑值3.当奔跑值大于50时可以对敌人（优先血量最低敌人）进行冲锋攻击，期间依然可以累计奔跑值 4.当骑兵冲锋后奔跑值降低为10点 5.骑兵选择冲撞某个敌人时会将中途的敌人击退，直到冲撞到目标敌人并将该敌人击退</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.优先攻击距离自己最近的敌人 2.每当自己周围存在一个己方单位时（自身100像素范围内），自身的防御力和攻击力提高3% 3.当自身100像素范围内存在弓箭手时，会为该范围内所有弓箭手抵挡1%的伤害，无时间刷新限制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>士兵系统</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能系统</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复药剂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>立即为范围内士兵恢复30%的最大生命值，并缓慢每秒恢复最大生命值1%的生命值，持续5秒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>狂暴药剂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>立即为范围内士兵增加以下buff：攻速提高30%，攻击力提高30%，世界持续5秒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100像素</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石药剂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>范围</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>价格（钻石为单位）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>立即召唤陨石对范围内敌人造成伤害（每个士兵40伤害）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -579,7 +628,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -638,7 +687,7 @@
         <v>10</v>
       </c>
       <c r="J2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -670,7 +719,7 @@
         <v>12</v>
       </c>
       <c r="J3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -699,15 +748,15 @@
         <v>45</v>
       </c>
       <c r="I4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -725,16 +774,16 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H5">
         <v>30</v>
       </c>
       <c r="I5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J5" t="s">
         <v>49</v>
-      </c>
-      <c r="J5" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -773,12 +822,79 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A3 D3 A2:B2 D2 A4:D4 H6:J6 F2:F4 A6:F6 A1:F1 H1:I1 H2:I2 H3:I3 H4" numberStoredAsText="1"/>
+    <ignoredError sqref="A3 D3 A2:B2 D2 A4:D4 H6:J6 F2:F4 A6:F6 B1:F1 H1:I1 H2:I2 H3:I3 H4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4644BC14-0351-4119-9620-1CB1EE49F3BA}">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
